--- a/daily_matches/job_matches_2026-06-23.xlsx
+++ b/daily_matches/job_matches_2026-06-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Business Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Fervo Energy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI</t>
+          <t>AI Engineer, Data Scientist, RAG, Redshift, BigQuery, Data Lake, Docker, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a21b8846522997bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c0394f69da3f3e0c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II, Full Stack &amp; AI</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, ChromaDB, OpenCV, Redshift, Docker, Kubernetes, CI/CD, Redshift, PostgreSQL</t>
+          <t>AI Engineer, Redshift, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Redshift, Tableau</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=306ab01c22f07a77</t>
+          <t>https://www.indeed.com/viewjob?jk=c0db552d42bcff54</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Applied Data Scientist / Machine Learning Engineer (Decision Intelligence)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>WorkWave™</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, Keras, MLflow, CI/CD, Snowflake, PySpark, MySQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Redshift, BigQuery, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96ebe8f7e65bd71</t>
+          <t>https://www.indeed.com/viewjob?jk=3b9e5345cb308db2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist/ Data Architect</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DDN</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Python</t>
+          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17be7a125f62a198</t>
+          <t>https://www.indeed.com/viewjob?jk=55ce642aeddf1f8f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Citian</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python</t>
+          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b974af9691c4f73</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c56ac0ca901604</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ML Software Engineer</t>
+          <t>Physical AI Engineering Consultant - Senior - Consulting - Open Location</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, Git, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, OpenCV, MLflow, AKS, CI/CD, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5e70fc43fe48407</t>
+          <t>https://www.indeed.com/viewjob?jk=bc25b2bad8f814d3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Application Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amy's Kitchen</t>
+          <t>Canon</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Synapse, CI/CD, Git, Databricks, Power BI, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, TensorFlow, BigQuery, Git, BigQuery, Hadoop, Tableau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b68f4aaf13a8c7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb47aab1b1be29e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer - Core Team</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>Userpilot</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, PyTorch, CI/CD, Git, PostgreSQL, Tableau, Python, SQL</t>
+          <t>S3, EC2, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b243686772972c6</t>
+          <t>https://www.indeed.com/viewjob?jk=262ca056c2ac8629</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Hugging Face, Prompt Engineering, Docker, Kubernetes, AKS, Git, PySpark, Python</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, TensorFlow, PyTorch, Synapse, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e408e8968c4aede3</t>
+          <t>https://www.indeed.com/viewjob?jk=5a47de0556207836</t>
         </is>
       </c>
     </row>
@@ -788,20 +788,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Apache Airflow, CI/CD, Git, PySpark, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, TensorFlow, PyTorch, Synapse, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2d03233369daa28</t>
+          <t>https://www.indeed.com/viewjob?jk=71471eb2f0ca66ee</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Microsoft Power Platform Solution Architect &amp; Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Matrix Global</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Databricks, Power BI, Python, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, TensorFlow, PyTorch, Synapse, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a491bd4ace0f6b28</t>
+          <t>https://www.indeed.com/viewjob?jk=dcbefe225a8949f7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Onsite</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WellSky</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Terraform, BigQuery, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, TensorFlow, PyTorch, Synapse, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d22952080ca1915</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf11ba0d77a73cd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Logistic Solutions, Inc.</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LangChain, LLaMA, Pinecone, FastAPI, Docker, PostgreSQL, MongoDB, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, TensorFlow, PyTorch, Synapse, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42bbc6ac6deab9f9</t>
+          <t>https://www.indeed.com/viewjob?jk=19a8c9ff8590af9c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Cloud Reliability Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VIANT TECHNOLOGY</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Rancho Cordova, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BigQuery, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, TensorFlow, PyTorch, Synapse, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520ee978a0e9c146</t>
+          <t>https://www.indeed.com/viewjob?jk=5114dfd1bcd93da6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Platform Data Reliability &amp; Automation)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, Terraform, Kafka, Cassandra, NoSQL, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, TensorFlow, PyTorch, Synapse, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b4127edb686f156</t>
+          <t>https://www.indeed.com/viewjob?jk=abad3a6a4924fd93</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, TensorFlow, PyTorch, Synapse, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99d0f76be4260ecc</t>
+          <t>https://www.indeed.com/viewjob?jk=6f3be0a5079c2d55</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>dv01</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, PyTorch, MLflow, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+          <t>RAG, Data Lake, CI/CD, Jenkins, Terraform, Git, Snowflake, Databricks, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79a6d2970b398f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f0995774c98d8f64</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer (Contract)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Civis Analytics</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Data Lake, CI/CD, GitHub Actions, Git, Snowflake, Databricks, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ed783e3c989e23</t>
+          <t>https://www.indeed.com/viewjob?jk=45ab8a36f01bb8e9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer (Contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Civis Analytics</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, S3, Redshift, Git, Databricks, Redshift, PySpark, Hadoop, Python</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce77bbab758a7093</t>
+          <t>https://www.indeed.com/viewjob?jk=82ecb174d2653ce3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer (Contract)</t>
+          <t>Software Engineer – Consumer Fraud Engineering - FDP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Civis Analytics</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Glue, Kinesis, Terraform, Git, PostgreSQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6ae6433d251c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ab4e0da5923841</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer (Contract)</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Civis Analytics</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, AKS, Snowflake, PySpark, Kafka, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f12b9b4fec1624db</t>
+          <t>https://www.indeed.com/viewjob?jk=df4f85c793d08d00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer (Contract)</t>
+          <t>Associate AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Civis Analytics</t>
+          <t>Wellfit Technologies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, Copilot, Prompt Engineering, FastAPI, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3e515c4aa61939</t>
+          <t>https://www.indeed.com/viewjob?jk=d3b0be2ce0b4cba4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Automation</t>
+          <t>SOLUTIONS ARCHITECT IV</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>giftHEALTH</t>
+          <t>Banda Group International</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, S3, EC2, CI/CD, Terraform, Git, Snowflake, Python</t>
+          <t>Generative AI, RAG, S3, MLflow, CI/CD, Terraform, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7b4cf3225aa1a46</t>
+          <t>https://www.indeed.com/viewjob?jk=533e64be9b9768db</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer, Connectivity Cloud</t>
+          <t>Software Engineer III - Database</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, EC2, Docker, Kubernetes, Git, Kafka, NoSQL, SQL, R, Java</t>
+          <t>RAG, CI/CD, Jenkins, Git, PostgreSQL, Cassandra, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752bd7b4ec4f835a</t>
+          <t>https://www.indeed.com/viewjob?jk=8b8e215e7d23df78</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>S3, EC2, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=855a2934e8d3c267</t>
+          <t>https://www.indeed.com/viewjob?jk=3ebb9ed44dd6b43d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer – Large Language Models &amp; Agentic Systems</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norfolk, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, Prompt Engineering, CI/CD, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786714eeaf0c6447</t>
+          <t>https://www.indeed.com/viewjob?jk=c184380a5df33b5b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Healthcare Data Scientist &amp; AI Solutions</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Biovid</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bristol, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Glue, Athena, FastAPI, Git, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, CI/CD, Jenkins, Git, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f887b41f78a3bcda</t>
+          <t>https://www.indeed.com/viewjob?jk=7920243ccd6b53ee</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer (Platform Data Reliability &amp; Automation)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, MongoDB, SQL, R, Java</t>
+          <t>Generative AI, RAG, Kubernetes, Terraform, Kafka, Cassandra, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8945d938630b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=162126f8a1836186</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior AI &amp; Business Operations Engineer</t>
+          <t>Software Engineer – Identity Shield</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Faraday Future</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Python, R, Java, Optimization, A/B Testing</t>
+          <t>Data Scientist, RAG, CI/CD, Terraform, Git, PostgreSQL, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b32480e72d8b872</t>
+          <t>https://www.indeed.com/viewjob?jk=3b89b133a8ea2e09</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Identity Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, R, Java, Scala, Optimization, A/B Testing</t>
+          <t>RAG, Copilot, S3, Kinesis, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2f1e070bd33fcc8</t>
+          <t>https://www.indeed.com/viewjob?jk=c39551869dd3c071</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Intern - Data Engineering - Corp</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, PySpark, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, RAG, CI/CD, Jenkins, Git, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ff48a7a0bbc69a</t>
+          <t>https://www.indeed.com/viewjob?jk=1ffe3a5ec1828269</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer, Full Stack</t>
+          <t>Software Engineer - Frontend</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PitchBook</t>
+          <t>Read AI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1567,11 +1567,11 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, FastAPI, Docker, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c4355a991f5ad5</t>
+          <t>https://www.indeed.com/viewjob?jk=480d799233d6bab9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Bioinformatics Engineer</t>
+          <t>AI Security Engineer (GRC)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, CI/CD, Git, Python, R, Scala, Optimization</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Hugging Face, Cortex, Git, Snowflake, SQL, R</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d0c0559e74f45e1</t>
+          <t>https://www.indeed.com/viewjob?jk=2bb1b25246fc1d17</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr Machine Learning Services Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FuGen IT Solutions</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,42 +1651,427 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356a0ca018ded67d</t>
+          <t>https://www.indeed.com/viewjob?jk=b1e83ed2ee441c23</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Snap Finance</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Glue, Athena, Redshift, Redshift, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca8022623046b6d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Operations Data Scientist</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>DIAMONDBACK ENERGY</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Midland, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf746c9cd8b62de6</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Generative AI Scientist II</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Cotiviti</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Mistral, TensorFlow, PyTorch, Keras, NLTK</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2516754588fd37cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FCP EURO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Milford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b2e7a2b148c2047</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Lowe's Home Improvement</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, XGBoost, MLflow, PySpark, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2721ad25b9b7692f</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PlusAI</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, S3, EC2, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49eb298174e16262</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AI engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Copilot, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3fa4f43ab99d382</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Overseas Contractor</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
         <v>10</v>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Python, SQL, R, Optimization, Bayesian, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9771f16e5aa19e</t>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Pinecone, Prompt Engineering, Kubernetes, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=592f35cd4c8b029c</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c898e0aee4a54220</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AI GRC Platform Enginner</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>RSI Security</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, Prompt Engineering, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d930e37f37ca804</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Research Software Engineer, First State AI Institute</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>University of Delaware</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Newark, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b88c2c39de65a331</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Copilot, Git, Hadoop, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7ce67cd8edcbc6d</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-23.xlsx
+++ b/daily_matches/job_matches_2026-06-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AD&amp;D Advanced Software Engineer Sr</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Cirrus Aircraft</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Duluth, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Databricks, Kafka</t>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, Docker, Kubernetes, CI/CD, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,129 +496,129 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=226455e4caa1635f</t>
+          <t>https://www.indeed.com/viewjob?jk=e69be16dc64cb06e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>AI Engineer - Onsite</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Glendale, WI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, LLaMA, Copilot, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes</t>
+          <t>AI Engineer, LangChain, RAG, Docker, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb31915c79f9367</t>
+          <t>https://www.indeed.com/viewjob?jk=3edd4adcb25e511c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>PMO Solutions Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>GREAT SOUTHWESTERN CONSTRUCTION</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Castle Rock, CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, PyTorch, XGBoost, AWS SageMaker, Docker, Kubernetes, Git, Snowflake, Databricks</t>
+          <t>RAG, Copilot, Prompt Engineering, Kubernetes, AKS, CI/CD, GitHub Actions, Git, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac4042b5ef7a75cc</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f2248e3f562b4c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Forma</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Terraform, Snowflake, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Kafka, PostgreSQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c44451a9ac3ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=79431165015e5a52</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Terraform, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, CI/CD, Terraform, Git, PostgreSQL, NoSQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bfb4ffdb59ad958</t>
+          <t>https://www.indeed.com/viewjob?jk=35eef562d5a6e1a0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Infrastructure &amp; Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Sargent &amp; Lundy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, SQL, R, Scala</t>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3c16c7da36cf54a</t>
+          <t>https://www.indeed.com/viewjob?jk=c6aad263f77591b1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Manger, AI and Analytics - Digital Product</t>
+          <t>Senior Software Engineer C#</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,77 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb11999f6200994</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AI Developer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24552ff1a90149e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AI Developer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53bc0b8960b68ff7</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0bb4b44a60a455</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-23.xlsx
+++ b/daily_matches/job_matches_2026-06-23.xlsx
@@ -468,130 +468,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD&amp;D Advanced Software Engineer Sr</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cirrus Aircraft</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Duluth, MN, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, OpenCV, Docker, Kubernetes, CI/CD, Jenkins, Git, Python</t>
+          <t>Data Scientist, Redshift, BigQuery, Docker, Kubernetes, CI/CD, Git, Snowflake, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69be16dc64cb06e</t>
+          <t>https://www.indeed.com/viewjob?jk=ea54597079589d42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer - Onsite</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Docker, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, MySQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3edd4adcb25e511c</t>
+          <t>https://www.indeed.com/viewjob?jk=34d52a48551c1790</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PMO Solutions Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GREAT SOUTHWESTERN CONSTRUCTION</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Castle Rock, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Kubernetes, AKS, CI/CD, GitHub Actions, Git, SQL, R</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Gemini, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f2248e3f562b4c</t>
+          <t>https://www.indeed.com/viewjob?jk=8b4e93d16c1f2907</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Web Application Engineer (Irvine, US)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Forma</t>
+          <t>Axon Networks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Kafka, PostgreSQL, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,112 +601,112 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79431165015e5a52</t>
+          <t>https://www.indeed.com/viewjob?jk=f78a4c688172469a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Engineer</t>
+          <t>Data Technical Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Rysun labs</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, Git, PostgreSQL, NoSQL, SQL, R, Scala, Optimization</t>
+          <t>Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, PySpark, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35eef562d5a6e1a0</t>
+          <t>https://www.indeed.com/viewjob?jk=43d82f1543437048</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Infrastructure &amp; Cloud Systems Engineer</t>
+          <t>Senior Software Engineer, Payments</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sargent &amp; Lundy</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aad263f77591b1</t>
+          <t>https://www.indeed.com/viewjob?jk=3572e441b7b83887</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer C#</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>PayActiv</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, SQL, R, Scala</t>
+          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, LightGBM, AWS SageMaker, Snowflake, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0bb4b44a60a455</t>
+          <t>https://www.indeed.com/viewjob?jk=0e17ae5e2e995c7f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-23.xlsx
+++ b/daily_matches/job_matches_2026-06-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Gen AI engineer 9+yrs exp ( W2 only)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>RigelSky</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, BigQuery, Docker, Kubernetes, CI/CD, Git, Snowflake, BigQuery, Redshift</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, ChromaDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea54597079589d42</t>
+          <t>https://www.indeed.com/viewjob?jk=faa9d897ef99b234</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Service Delivery Center, AI Developer - Senior</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, MySQL, NoSQL, Python</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, AWS SageMaker, Azure ML, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d52a48551c1790</t>
+          <t>https://www.indeed.com/viewjob?jk=c00d2a18ab03e4d9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, Gemini, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes</t>
+          <t>Data Scientist, RAG, S3, BigQuery, Data Lake, Git, Snowflake, Databricks, BigQuery, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b4e93d16c1f2907</t>
+          <t>https://www.indeed.com/viewjob?jk=933ab6807d4d8842</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Web Application Engineer (Irvine, US)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Axon Networks</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Copilot, S3, Glue, Athena, Docker, Kubernetes, CI/CD, Git, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78a4c688172469a</t>
+          <t>https://www.indeed.com/viewjob?jk=d633e19b2a078926</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Technical Architect</t>
+          <t>AI Engineer (Data Scientist)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>Zions Bancorporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, PySpark, Kafka, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, PyTorch, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d82f1543437048</t>
+          <t>https://www.indeed.com/viewjob?jk=f32877cedcf85598</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Payments</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,917 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3572e441b7b83887</t>
+          <t>https://www.indeed.com/viewjob?jk=cf87bc8d4644326b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PayActiv</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff3e7b36fe0eff89</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d3309aad7167c95</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af85de8b2a3ab880</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Berkeley, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff044df5cff76741</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=544039c92cd95980</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LPL Financial</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, Glue, Athena, Docker, Kubernetes, CI/CD, Git, PySpark</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50c0af65411f0014</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Faro Health Inc.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e75e8818d349ed7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Zions Bancorporation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Midvale, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, MongoDB, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9527693e3f8ed2cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Altom Transport, Inc.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>13.3</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, LightGBM, AWS SageMaker, Snowflake, Tableau, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0e17ae5e2e995c7f</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=189e85b9aadd7294</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cetera Financial Group</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Snowflake, Databricks, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=177f839eafc70423</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Aktra Inc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Jenkins, Git, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=400a7e2db46374c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer - Claims Technology</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fd3b089b8e85de9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer - Claims Technology</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=047ca970efc97204</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer - Claims Technology</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a768e6f7c8f1f47f</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer - Claims Technology</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Portsmouth, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c64b08e271f522f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer - Claims Technology</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26fefc6c4e81a9d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CCC Intelligent Solutions</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, Git, Kafka, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4645fea57c860db</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a119a134f1b9aa5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>American Public Media</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, CI/CD, Git, Databricks, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8390039bc78bb15</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Cloud DevOps 4</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Sioux Falls, SD, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af03686e6c6cf6a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Databricks, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7488931bef280ccd</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Cloud DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Regions Financial</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Generative AI, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4c94314064b7f8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI Python Architect</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, Azure ML, Data Lake, AKS, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a26f538388fb7042</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sr DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>QVC</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>West Chester, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8aebe05dc333a974</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a093fe589c48d4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Resmed</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8efe220403383bd</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-23.xlsx
+++ b/daily_matches/job_matches_2026-06-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gen AI engineer 9+yrs exp ( W2 only)</t>
+          <t>AI Automation Developer &amp; Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RigelSky</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>36.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, ChromaDB</t>
+          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, S3, Glue, Redshift, BigQuery, Synapse</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa9d897ef99b234</t>
+          <t>https://www.indeed.com/viewjob?jk=8315a758255bb079</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Service Delivery Center, AI Developer - Senior</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, AWS SageMaker, Azure ML, Docker</t>
+          <t>RAG, BigQuery, Docker, Kubernetes, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Git, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00d2a18ab03e4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=727cbe7cc2d8d727</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, BigQuery, Data Lake, Git, Snowflake, Databricks, BigQuery, PySpark</t>
+          <t>Generative AI, S3, EC2, Glue, Redshift, Apache Airflow, CI/CD, Redshift, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933ab6807d4d8842</t>
+          <t>https://www.indeed.com/viewjob?jk=d917a7b6e943564a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, Athena, Docker, Kubernetes, CI/CD, Git, PySpark</t>
+          <t>RAG, Copilot, Prompt Engineering, S3, Kubernetes, CI/CD, GitHub Actions, Git, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d633e19b2a078926</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a9951c27680605</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer (Data Scientist)</t>
+          <t>Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>ClearpointCo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, PyTorch, FastAPI, Docker, Kubernetes</t>
+          <t>Copilot, Synapse, Dataflow, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f32877cedcf85598</t>
+          <t>https://www.indeed.com/viewjob?jk=35d60eb49ba0667d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Accertify, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Itasca, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
+          <t>AI Engineer, Data Scientist, RAG, Hugging Face, Pinecone, Prompt Engineering, Kubernetes, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf87bc8d4644326b</t>
+          <t>https://www.indeed.com/viewjob?jk=5447c2e70539df8f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Mid Level Fullstack Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
+          <t>LangChain, RAG, Copilot, Docker, CI/CD, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e7b36fe0eff89</t>
+          <t>https://www.indeed.com/viewjob?jk=4679927fbe368451</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Associate DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Keenfinity</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fairport, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3309aad7167c95</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd7c7be3ac15aed</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Sr. Fullstack Engineer (Heavy backend/ AI-Assisted)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
+          <t>RAG, Docker, CI/CD, Jenkins, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af85de8b2a3ab880</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8e641f619c036a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
+          <t>Data Scientist, Generative AI, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff044df5cff76741</t>
+          <t>https://www.indeed.com/viewjob?jk=9e2c9f35ff382a35</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
+          <t>Data Scientist, Generative AI, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544039c92cd95980</t>
+          <t>https://www.indeed.com/viewjob?jk=de24657d0818c9b0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, Athena, Docker, Kubernetes, CI/CD, Git, PySpark</t>
+          <t>Data Scientist, Generative AI, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c0af65411f0014</t>
+          <t>https://www.indeed.com/viewjob?jk=343cbd89db3882c4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, Generative AI, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75e8818d349ed7c</t>
+          <t>https://www.indeed.com/viewjob?jk=13987f63f23fd7da</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, MongoDB, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9527693e3f8ed2cc</t>
+          <t>https://www.indeed.com/viewjob?jk=2a5f8c13af99e023</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189e85b9aadd7294</t>
+          <t>https://www.indeed.com/viewjob?jk=e55293dd45f18f28</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cetera Financial Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Snowflake, Databricks, Kafka, Python</t>
+          <t>Data Scientist, Generative AI, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177f839eafc70423</t>
+          <t>https://www.indeed.com/viewjob?jk=0001915d1d2e584f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Senior Business Data Analyst - Ad Operations - Arity</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aktra Inc</t>
+          <t>Arity</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Jenkins, Git, Kafka, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=400a7e2db46374c1</t>
+          <t>https://www.indeed.com/viewjob?jk=9d1d909ff1a3d818</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer - Claims Technology</t>
+          <t>Sr. IT Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Xai</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R, Java</t>
+          <t>RAG, Kafka, Hadoop, MySQL, MongoDB, Cassandra, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd3b089b8e85de9</t>
+          <t>https://www.indeed.com/viewjob?jk=162be4aca96e45e2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer - Claims Technology</t>
+          <t>Senior AI Engineer - Agentic Workflow</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, PyTorch, Docker, Kubernetes, Python, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047ca970efc97204</t>
+          <t>https://www.indeed.com/viewjob?jk=f3801919a01205f6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer - Claims Technology</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>WOW! Internet Cable and Phone</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R, Java</t>
+          <t>RAG, Copilot, S3, EC2, CI/CD, Git, R, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a768e6f7c8f1f47f</t>
+          <t>https://www.indeed.com/viewjob?jk=171009d1c07d4989</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer - Claims Technology</t>
+          <t>Sr. Fullstack Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R, Java</t>
+          <t>RAG, Docker, Jenkins, Kafka, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c64b08e271f522f6</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5d09010963ef59</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer - Claims Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R, Java</t>
+          <t>RAG, BigQuery, Dataflow, Docker, Git, BigQuery, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fefc6c4e81a9d3</t>
+          <t>https://www.indeed.com/viewjob?jk=44553d8c9642b4ed</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>829 Studios</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Git, Kafka, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
+          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4645fea57c860db</t>
+          <t>https://www.indeed.com/viewjob?jk=f8312cf87c5ad3b8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>GenAI Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a119a134f1b9aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=51f0b55b1cb72310</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GenAI Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>American Public Media</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, CI/CD, Git, Databricks, Power BI, Python, SQL, R</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8390039bc78bb15</t>
+          <t>https://www.indeed.com/viewjob?jk=b651b10d7a68a370</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud DevOps 4</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>Generative AI, Prompt Engineering, S3, Docker, Kubernetes, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af03686e6c6cf6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=487e40a26f3b43ea</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Solutions Architect (AWS, Big Data, Data Engineering)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>Kinesis, Apache Airflow, Terraform, Databricks, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7488931bef280ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=05f3c602815dd894</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Generative AI, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, Git, Hadoop, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c94314064b7f8f</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a5383caa636f90</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Python Architect</t>
+          <t>Senior Applied AI/ML Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>NobleAI</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Azure ML, Data Lake, AKS, Git, Python, R, Optimization</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Keras, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a26f538388fb7042</t>
+          <t>https://www.indeed.com/viewjob?jk=0f3669c93b6bd4f2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Software Engineer, AI Agents &amp; Generative AI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>Vantor</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>Generative AI, LangChain, RAG, Gemini, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aebe05dc333a974</t>
+          <t>https://www.indeed.com/viewjob?jk=a088e225bddb1a63</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, AI Agents &amp; Generative AI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vantor</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
+          <t>Generative AI, LangChain, RAG, Gemini, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a093fe589c48d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=a1a2297199ab7341</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Mgr. Software Engineering-(AI)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Resmed</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,52 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
+          <t>LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8efe220403383bd</t>
+          <t>https://www.indeed.com/viewjob?jk=e8ed9b91eafc5b96</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer (React + .NET/Java, Shopify)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>DATAMAXIS</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Gemini, Copilot, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61348b611b1c6966</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-23.xlsx
+++ b/daily_matches/job_matches_2026-06-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Automation Developer &amp; Data Scientist</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>36.7</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, S3, Glue, Redshift, BigQuery, Synapse</t>
+          <t>Data Scientist, RAG, Synapse, CI/CD, Git, Databricks, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8315a758255bb079</t>
+          <t>https://www.indeed.com/viewjob?jk=a11738879dff288c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.3</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, Kubernetes, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Git, BigQuery</t>
+          <t>RAG, Gemini, Copilot, S3, EC2, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727cbe7cc2d8d727</t>
+          <t>https://www.indeed.com/viewjob?jk=7731267ec6f619b8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Java Cloud Migration Engineer (OpenShift / Infrastructure &amp; Application Modernization)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, S3, EC2, Glue, Redshift, Apache Airflow, CI/CD, Redshift, PySpark, NoSQL</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MongoDB, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d917a7b6e943564a</t>
+          <t>https://www.indeed.com/viewjob?jk=d63f649b6edb613b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>WelbeHealth</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, Kubernetes, CI/CD, GitHub Actions, Git, MongoDB, NoSQL</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Docker, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a9951c27680605</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed68378c3485f49</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Engineer</t>
+          <t>Senior Software Engineer - Authentication</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ClearpointCo</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Copilot, Synapse, Dataflow, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>RAG, S3, Kinesis, Docker, Kubernetes, CI/CD, Git, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d60eb49ba0667d</t>
+          <t>https://www.indeed.com/viewjob?jk=1dfb62e4da91a70a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Accertify, Inc.</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Itasca, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Hugging Face, Pinecone, Prompt Engineering, Kubernetes, CI/CD, Python, SQL</t>
+          <t>RAG, CI/CD, Git, Snowflake, Databricks, Kafka, PostgreSQL, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5447c2e70539df8f</t>
+          <t>https://www.indeed.com/viewjob?jk=fff180e33e1711ff</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mid Level Fullstack Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Docker, CI/CD, Kafka, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4679927fbe368451</t>
+          <t>https://www.indeed.com/viewjob?jk=b063a70a1f68f24c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate DevOps Software Engineer</t>
+          <t>Analyst Databricks</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Keenfinity</t>
+          <t>Hilton Grand Vacations</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fairport, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+          <t>MLflow, CI/CD, Git, Databricks, PySpark, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd7c7be3ac15aed</t>
+          <t>https://www.indeed.com/viewjob?jk=c254b2804a86227c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Engineer (Heavy backend/ AI-Assisted)</t>
+          <t>Senior Software Engineer, Product Foundations</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Justworks</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, Kafka, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8e641f619c036a</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7c59bba3119305</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git, R</t>
+          <t>Data Scientist, RAG, Docker, Terraform, Snowflake, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e2c9f35ff382a35</t>
+          <t>https://www.indeed.com/viewjob?jk=57316bd44c07be7d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
+          <t>Senior Performance Advertising Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>PubMatic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git, R</t>
+          <t>BigQuery, Git, Snowflake, BigQuery, Kafka, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de24657d0818c9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=dbeea737c3c39dab</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
+          <t>Senior Performance Advertising Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>PubMatic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git, R</t>
+          <t>BigQuery, Git, Snowflake, BigQuery, Kafka, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=343cbd89db3882c4</t>
+          <t>https://www.indeed.com/viewjob?jk=acd485cfb174393d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
+          <t>NetSuite Application Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Bandwidth</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git, R</t>
+          <t>Generative AI, LangChain, RAG, S3, Snowflake, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13987f63f23fd7da</t>
+          <t>https://www.indeed.com/viewjob?jk=6bca5e46e5cdda28</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
+          <t>Senior QA Automation Engineer with AI and Playwright experience</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git, R</t>
+          <t>Generative AI, RAG, Copilot, CI/CD, GitHub Actions, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5f8c13af99e023</t>
+          <t>https://www.indeed.com/viewjob?jk=e28a06abf5e7e9c5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
+          <t>Jr. Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Focus Camera</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git, R</t>
+          <t>Data Scientist, Git, MySQL, Power BI, Python, SQL, R, Scala, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e55293dd45f18f28</t>
+          <t>https://www.indeed.com/viewjob?jk=c439e9c8611b4f5c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
+          <t>Senior .Net Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git, R</t>
+          <t>Generative AI, RAG, Gemini, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0001915d1d2e584f</t>
+          <t>https://www.indeed.com/viewjob?jk=e74fda4c7b8f32d2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Business Data Analyst - Ad Operations - Arity</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Arity</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, CI/CD, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d1d909ff1a3d818</t>
+          <t>https://www.indeed.com/viewjob?jk=b48cb24418e7f0e2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. IT Data Engineer</t>
+          <t>Full Stack Developer III</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Xai</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Kafka, Hadoop, MySQL, MongoDB, Cassandra, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Docker, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=162be4aca96e45e2</t>
+          <t>https://www.indeed.com/viewjob?jk=31c993505a078ae2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - Agentic Workflow</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, PyTorch, Docker, Kubernetes, Python, R, Java</t>
+          <t>Data Scientist, RAG, Kubernetes, Snowflake, Databricks, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3801919a01205f6</t>
+          <t>https://www.indeed.com/viewjob?jk=952be095ea29d41f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Cloud Network Engineer II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WOW! Internet Cable and Phone</t>
+          <t>Amerisure</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, CI/CD, Git, R, Scala, Optimization, A/B Testing</t>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,462 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171009d1c07d4989</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Sr. Fullstack Developer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Intone Networks</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Jenkins, Kafka, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5d09010963ef59</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Hollstadt Consulting</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>MN, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Dataflow, Docker, Git, BigQuery, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44553d8c9642b4ed</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>829 Studios</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f8312cf87c5ad3b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>GenAI Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=51f0b55b1cb72310</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>GenAI Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b651b10d7a68a370</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Sr. SW Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Foster City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Generative AI, Prompt Engineering, S3, Docker, Kubernetes, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=487e40a26f3b43ea</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Data Solutions Architect (AWS, Big Data, Data Engineering)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Auburn Hills, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Kinesis, Apache Airflow, Terraform, Databricks, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=05f3c602815dd894</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Epsilon</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, Hadoop, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a5383caa636f90</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Applied AI/ML Scientist</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>NobleAI</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Keras, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f3669c93b6bd4f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Software Engineer, AI Agents &amp; Generative AI</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Vantor</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Gemini, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a088e225bddb1a63</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Software Engineer, AI Agents &amp; Generative AI</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Vantor</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Westminster, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Gemini, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a2297199ab7341</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Mgr. Software Engineering-(AI)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>UKG</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Sunrise, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ed9b91eafc5b96</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Full Stack Software Engineer (React + .NET/Java, Shopify)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>DATAMAXIS</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Dearborn, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Gemini, Copilot, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61348b611b1c6966</t>
+          <t>https://www.indeed.com/viewjob?jk=98627ffbde1c523b</t>
         </is>
       </c>
     </row>
